--- a/output/yearly_total_coral_cover_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_77_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254198827410467</v>
+        <v>1.274599544704715</v>
       </c>
       <c r="C3" t="n">
-        <v>4.620484523607194</v>
+        <v>4.584238398366402</v>
       </c>
       <c r="D3" t="n">
-        <v>6.082884325755271</v>
+        <v>6.179242862927095</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95756767677293</v>
+        <v>12.03808080599821</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.374991710937778</v>
+        <v>1.434530715769073</v>
       </c>
       <c r="C4" t="n">
-        <v>5.090319688395931</v>
+        <v>4.991120318531064</v>
       </c>
       <c r="D4" t="n">
-        <v>6.305358951800491</v>
+        <v>6.427967797771132</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7706703511342</v>
+        <v>12.85361883207127</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.53694881349578</v>
+        <v>1.647923378629601</v>
       </c>
       <c r="C5" t="n">
-        <v>5.671346695312378</v>
+        <v>5.502604053164315</v>
       </c>
       <c r="D5" t="n">
-        <v>6.614492233897911</v>
+        <v>6.778211635843496</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82278774270607</v>
+        <v>13.92873906763741</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739465195644017</v>
+        <v>1.887290787006647</v>
       </c>
       <c r="C6" t="n">
-        <v>6.375420174193216</v>
+        <v>6.126633384178262</v>
       </c>
       <c r="D6" t="n">
-        <v>6.918822187515151</v>
+        <v>7.167266376907514</v>
       </c>
       <c r="E6" t="n">
-        <v>15.03370755735239</v>
+        <v>15.18119054809242</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.973118098835662</v>
+        <v>2.150636933344347</v>
       </c>
       <c r="C7" t="n">
-        <v>7.209006027905086</v>
+        <v>6.897249725789638</v>
       </c>
       <c r="D7" t="n">
-        <v>7.209794448233515</v>
+        <v>7.573988887397993</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39191857497426</v>
+        <v>16.62187554653198</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.232907941106959</v>
+        <v>1.362368003012196</v>
       </c>
       <c r="C8" t="n">
-        <v>4.816954773508472</v>
+        <v>4.611614904674686</v>
       </c>
       <c r="D8" t="n">
-        <v>5.375760604144797</v>
+        <v>5.778071194347015</v>
       </c>
       <c r="E8" t="n">
-        <v>11.42562331876023</v>
+        <v>11.7520541020339</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.579975403813586</v>
+        <v>1.739298059951791</v>
       </c>
       <c r="C9" t="n">
-        <v>5.892466583675248</v>
+        <v>5.669116825831475</v>
       </c>
       <c r="D9" t="n">
-        <v>5.792078058962406</v>
+        <v>6.320037807916248</v>
       </c>
       <c r="E9" t="n">
-        <v>13.26452004645124</v>
+        <v>13.72845269369951</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.956251322394666</v>
+        <v>2.135156380074273</v>
       </c>
       <c r="C10" t="n">
-        <v>7.163895657749727</v>
+        <v>6.915427284082758</v>
       </c>
       <c r="D10" t="n">
-        <v>6.216457127680318</v>
+        <v>6.833476915857106</v>
       </c>
       <c r="E10" t="n">
-        <v>15.33660410782471</v>
+        <v>15.88406058001414</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.351426945002411</v>
+        <v>2.534269641933646</v>
       </c>
       <c r="C11" t="n">
-        <v>8.580874753867873</v>
+        <v>8.275207148907237</v>
       </c>
       <c r="D11" t="n">
-        <v>6.67603586826824</v>
+        <v>7.355414897768665</v>
       </c>
       <c r="E11" t="n">
-        <v>17.60833756713852</v>
+        <v>18.16489168860955</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.752557365933492</v>
+        <v>2.950324461913397</v>
       </c>
       <c r="C12" t="n">
-        <v>10.14741574925995</v>
+        <v>9.72084988383868</v>
       </c>
       <c r="D12" t="n">
-        <v>7.093038695402541</v>
+        <v>7.836975088187399</v>
       </c>
       <c r="E12" t="n">
-        <v>19.99301181059598</v>
+        <v>20.50814943393948</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.150495490693665</v>
+        <v>3.35642759965251</v>
       </c>
       <c r="C13" t="n">
-        <v>11.77169196607962</v>
+        <v>11.20961833164498</v>
       </c>
       <c r="D13" t="n">
-        <v>7.480574128994705</v>
+        <v>8.331621511150054</v>
       </c>
       <c r="E13" t="n">
-        <v>22.40276158576799</v>
+        <v>22.89766744244755</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.807947302232756</v>
+        <v>1.938323397356733</v>
       </c>
       <c r="C14" t="n">
-        <v>8.31014088727572</v>
+        <v>7.812011919617931</v>
       </c>
       <c r="D14" t="n">
-        <v>5.70057694957136</v>
+        <v>6.29377836490841</v>
       </c>
       <c r="E14" t="n">
-        <v>15.81866513907984</v>
+        <v>16.04411368188307</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.884867234860494</v>
+        <v>2.011895570312989</v>
       </c>
       <c r="C15" t="n">
-        <v>9.063455535698385</v>
+        <v>8.460112666576464</v>
       </c>
       <c r="D15" t="n">
-        <v>5.648897750419808</v>
+        <v>6.308759834875216</v>
       </c>
       <c r="E15" t="n">
-        <v>16.59722052097869</v>
+        <v>16.78076807176467</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.220575862327691</v>
+        <v>2.368593963696982</v>
       </c>
       <c r="C16" t="n">
-        <v>10.82378807427517</v>
+        <v>10.02848407654187</v>
       </c>
       <c r="D16" t="n">
-        <v>6.067770225913751</v>
+        <v>6.802637834973617</v>
       </c>
       <c r="E16" t="n">
-        <v>19.11213416251661</v>
+        <v>19.19971587521247</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.799504271976234</v>
+        <v>1.920298509506762</v>
       </c>
       <c r="C17" t="n">
-        <v>10.10784856095318</v>
+        <v>9.325739252364961</v>
       </c>
       <c r="D17" t="n">
-        <v>5.589610006560342</v>
+        <v>6.326843627587443</v>
       </c>
       <c r="E17" t="n">
-        <v>17.49696283948976</v>
+        <v>17.57288138945917</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.079449629842212</v>
+        <v>2.216030370457028</v>
       </c>
       <c r="C18" t="n">
-        <v>11.92758665311394</v>
+        <v>10.88829871592123</v>
       </c>
       <c r="D18" t="n">
-        <v>5.973326096765208</v>
+        <v>6.764192594875311</v>
       </c>
       <c r="E18" t="n">
-        <v>19.98036237972136</v>
+        <v>19.86852168125357</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.109432204729909</v>
+        <v>2.246032580298811</v>
       </c>
       <c r="C19" t="n">
-        <v>12.87093820464766</v>
+        <v>11.66157229517123</v>
       </c>
       <c r="D19" t="n">
-        <v>6.030090749024758</v>
+        <v>6.864173781075808</v>
       </c>
       <c r="E19" t="n">
-        <v>21.01046115840233</v>
+        <v>20.77177865654584</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.373208177906942</v>
+        <v>2.525349619634071</v>
       </c>
       <c r="C20" t="n">
-        <v>14.87682547901066</v>
+        <v>13.41106633909313</v>
       </c>
       <c r="D20" t="n">
-        <v>6.458564717066237</v>
+        <v>7.3149825093889</v>
       </c>
       <c r="E20" t="n">
-        <v>23.70859837398384</v>
+        <v>23.2513984681161</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.423534171157875</v>
+        <v>1.514090579397601</v>
       </c>
       <c r="C21" t="n">
-        <v>10.98634585914436</v>
+        <v>9.846379694881129</v>
       </c>
       <c r="D21" t="n">
-        <v>5.367067436961675</v>
+        <v>6.090114803662408</v>
       </c>
       <c r="E21" t="n">
-        <v>17.77694746726391</v>
+        <v>17.45058507794114</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_77_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.274599544704715</v>
+        <v>1.251577561040127</v>
       </c>
       <c r="C3" t="n">
-        <v>4.584238398366402</v>
+        <v>4.675972903851225</v>
       </c>
       <c r="D3" t="n">
-        <v>6.179242862927095</v>
+        <v>6.040129213235323</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03808080599821</v>
+        <v>11.96767967812668</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.434530715769073</v>
+        <v>1.370140140086638</v>
       </c>
       <c r="C4" t="n">
-        <v>4.991120318531064</v>
+        <v>5.274280295982842</v>
       </c>
       <c r="D4" t="n">
-        <v>6.427967797771132</v>
+        <v>6.210197942452299</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85361883207127</v>
+        <v>12.85461837852178</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.647923378629601</v>
+        <v>1.528124535064196</v>
       </c>
       <c r="C5" t="n">
-        <v>5.502604053164315</v>
+        <v>6.096451013941035</v>
       </c>
       <c r="D5" t="n">
-        <v>6.778211635843496</v>
+        <v>6.404345348009251</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92873906763741</v>
+        <v>14.02892089701448</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.887290787006647</v>
+        <v>1.715175544618027</v>
       </c>
       <c r="C6" t="n">
-        <v>6.126633384178262</v>
+        <v>7.140541776268947</v>
       </c>
       <c r="D6" t="n">
-        <v>7.167266376907514</v>
+        <v>6.644405668872615</v>
       </c>
       <c r="E6" t="n">
-        <v>15.18119054809242</v>
+        <v>15.50012298975959</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.150636933344347</v>
+        <v>1.914868996420358</v>
       </c>
       <c r="C7" t="n">
-        <v>6.897249725789638</v>
+        <v>8.355817748450665</v>
       </c>
       <c r="D7" t="n">
-        <v>7.573988887397993</v>
+        <v>6.848224885096799</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62187554653198</v>
+        <v>17.11891162996782</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.362368003012196</v>
+        <v>1.134341696701516</v>
       </c>
       <c r="C8" t="n">
-        <v>4.611614904674686</v>
+        <v>5.996629391514199</v>
       </c>
       <c r="D8" t="n">
-        <v>5.778071194347015</v>
+        <v>5.007036720209482</v>
       </c>
       <c r="E8" t="n">
-        <v>11.7520541020339</v>
+        <v>12.1380078084252</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.739298059951791</v>
+        <v>1.39842226546284</v>
       </c>
       <c r="C9" t="n">
-        <v>5.669116825831475</v>
+        <v>7.43797972749786</v>
       </c>
       <c r="D9" t="n">
-        <v>6.320037807916248</v>
+        <v>5.291656764751735</v>
       </c>
       <c r="E9" t="n">
-        <v>13.72845269369951</v>
+        <v>14.12805875771243</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135156380074273</v>
+        <v>1.671407523939141</v>
       </c>
       <c r="C10" t="n">
-        <v>6.915427284082758</v>
+        <v>9.01635804864892</v>
       </c>
       <c r="D10" t="n">
-        <v>6.833476915857106</v>
+        <v>5.668946730953557</v>
       </c>
       <c r="E10" t="n">
-        <v>15.88406058001414</v>
+        <v>16.35671230354162</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.534269641933646</v>
+        <v>1.954456399391452</v>
       </c>
       <c r="C11" t="n">
-        <v>8.275207148907237</v>
+        <v>10.72951148902077</v>
       </c>
       <c r="D11" t="n">
-        <v>7.355414897768665</v>
+        <v>6.057273682377518</v>
       </c>
       <c r="E11" t="n">
-        <v>18.16489168860955</v>
+        <v>18.74124157078975</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.950324461913397</v>
+        <v>2.225812486647734</v>
       </c>
       <c r="C12" t="n">
-        <v>9.72084988383868</v>
+        <v>12.53640768895696</v>
       </c>
       <c r="D12" t="n">
-        <v>7.836975088187399</v>
+        <v>6.490184333832754</v>
       </c>
       <c r="E12" t="n">
-        <v>20.50814943393948</v>
+        <v>21.25240450943745</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.35642759965251</v>
+        <v>2.485556740942727</v>
       </c>
       <c r="C13" t="n">
-        <v>11.20961833164498</v>
+        <v>14.42457436936547</v>
       </c>
       <c r="D13" t="n">
-        <v>8.331621511150054</v>
+        <v>6.810294285608448</v>
       </c>
       <c r="E13" t="n">
-        <v>22.89766744244755</v>
+        <v>23.72042539591665</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.938323397356733</v>
+        <v>1.44212847267631</v>
       </c>
       <c r="C14" t="n">
-        <v>7.812011919617931</v>
+        <v>10.18549498688206</v>
       </c>
       <c r="D14" t="n">
-        <v>6.29377836490841</v>
+        <v>5.23641645248051</v>
       </c>
       <c r="E14" t="n">
-        <v>16.04411368188307</v>
+        <v>16.86403991203888</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.011895570312989</v>
+        <v>1.452839340129642</v>
       </c>
       <c r="C15" t="n">
-        <v>8.460112666576464</v>
+        <v>11.06536673185918</v>
       </c>
       <c r="D15" t="n">
-        <v>6.308759834875216</v>
+        <v>5.169382719234537</v>
       </c>
       <c r="E15" t="n">
-        <v>16.78076807176467</v>
+        <v>17.68758879122336</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.368593963696982</v>
+        <v>1.665770599703733</v>
       </c>
       <c r="C16" t="n">
-        <v>10.02848407654187</v>
+        <v>13.13685438781995</v>
       </c>
       <c r="D16" t="n">
-        <v>6.802637834973617</v>
+        <v>5.52162397804125</v>
       </c>
       <c r="E16" t="n">
-        <v>19.19971587521247</v>
+        <v>20.32424896556493</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.920298509506762</v>
+        <v>1.322031276015798</v>
       </c>
       <c r="C17" t="n">
-        <v>9.325739252364961</v>
+        <v>12.07372961636812</v>
       </c>
       <c r="D17" t="n">
-        <v>6.326843627587443</v>
+        <v>5.056540638108409</v>
       </c>
       <c r="E17" t="n">
-        <v>17.57288138945917</v>
+        <v>18.45230153049233</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.216030370457028</v>
+        <v>1.494288728202943</v>
       </c>
       <c r="C18" t="n">
-        <v>10.88829871592123</v>
+        <v>14.20442647637202</v>
       </c>
       <c r="D18" t="n">
-        <v>6.764192594875311</v>
+        <v>5.339666858536146</v>
       </c>
       <c r="E18" t="n">
-        <v>19.86852168125357</v>
+        <v>21.03838206311111</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.246032580298811</v>
+        <v>1.483479685979185</v>
       </c>
       <c r="C19" t="n">
-        <v>11.66157229517123</v>
+        <v>15.29626736817307</v>
       </c>
       <c r="D19" t="n">
-        <v>6.864173781075808</v>
+        <v>5.364279273481615</v>
       </c>
       <c r="E19" t="n">
-        <v>20.77177865654584</v>
+        <v>22.14402632763387</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.525349619634071</v>
+        <v>1.634040513902476</v>
       </c>
       <c r="C20" t="n">
-        <v>13.41106633909313</v>
+        <v>17.7208405859662</v>
       </c>
       <c r="D20" t="n">
-        <v>7.3149825093889</v>
+        <v>5.696316164534928</v>
       </c>
       <c r="E20" t="n">
-        <v>23.2513984681161</v>
+        <v>25.0511972644036</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.514090579397601</v>
+        <v>0.9651561680450393</v>
       </c>
       <c r="C21" t="n">
-        <v>9.846379694881129</v>
+        <v>13.13384042236791</v>
       </c>
       <c r="D21" t="n">
-        <v>6.090114803662408</v>
+        <v>4.718868515232719</v>
       </c>
       <c r="E21" t="n">
-        <v>17.45058507794114</v>
+        <v>18.81786510564567</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_77_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251577561040127</v>
+        <v>2.606824383493043</v>
       </c>
       <c r="C3" t="n">
-        <v>4.675972903851225</v>
+        <v>7.867998160547634</v>
       </c>
       <c r="D3" t="n">
-        <v>6.040129213235323</v>
+        <v>8.155081459924402</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96767967812668</v>
+        <v>18.62990400396508</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370140140086638</v>
+        <v>1.10736771368112</v>
       </c>
       <c r="C4" t="n">
-        <v>5.274280295982842</v>
+        <v>4.905906689557258</v>
       </c>
       <c r="D4" t="n">
-        <v>6.210197942452299</v>
+        <v>5.90767567816368</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85461837852178</v>
+        <v>11.92095008140206</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.528124535064196</v>
+        <v>1.231989205954646</v>
       </c>
       <c r="C5" t="n">
-        <v>6.096451013941035</v>
+        <v>6.003482432457256</v>
       </c>
       <c r="D5" t="n">
-        <v>6.404345348009251</v>
+        <v>6.205469454428505</v>
       </c>
       <c r="E5" t="n">
-        <v>14.02892089701448</v>
+        <v>13.44094109284041</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.715175544618027</v>
+        <v>1.371299326895138</v>
       </c>
       <c r="C6" t="n">
-        <v>7.140541776268947</v>
+        <v>7.407602038664392</v>
       </c>
       <c r="D6" t="n">
-        <v>6.644405668872615</v>
+        <v>6.590672619155407</v>
       </c>
       <c r="E6" t="n">
-        <v>15.50012298975959</v>
+        <v>15.36957398471494</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.914868996420358</v>
+        <v>1.51476403136733</v>
       </c>
       <c r="C7" t="n">
-        <v>8.355817748450665</v>
+        <v>9.063511894871951</v>
       </c>
       <c r="D7" t="n">
-        <v>6.848224885096799</v>
+        <v>6.963557335604256</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11891162996782</v>
+        <v>17.54183326184354</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.134341696701516</v>
+        <v>1.653577851930407</v>
       </c>
       <c r="C8" t="n">
-        <v>5.996629391514199</v>
+        <v>10.89918946666037</v>
       </c>
       <c r="D8" t="n">
-        <v>5.007036720209482</v>
+        <v>7.340049122325937</v>
       </c>
       <c r="E8" t="n">
-        <v>12.1380078084252</v>
+        <v>19.89281644091671</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.39842226546284</v>
+        <v>1.771763085922676</v>
       </c>
       <c r="C9" t="n">
-        <v>7.43797972749786</v>
+        <v>12.83328496538324</v>
       </c>
       <c r="D9" t="n">
-        <v>5.291656764751735</v>
+        <v>7.706273684352566</v>
       </c>
       <c r="E9" t="n">
-        <v>14.12805875771243</v>
+        <v>22.31132173565848</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.671407523939141</v>
+        <v>1.087511384425319</v>
       </c>
       <c r="C10" t="n">
-        <v>9.01635804864892</v>
+        <v>9.035534630989606</v>
       </c>
       <c r="D10" t="n">
-        <v>5.668946730953557</v>
+        <v>6.035509996352201</v>
       </c>
       <c r="E10" t="n">
-        <v>16.35671230354162</v>
+        <v>16.15855601176712</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954456399391452</v>
+        <v>1.01897557719185</v>
       </c>
       <c r="C11" t="n">
-        <v>10.72951148902077</v>
+        <v>10.02050246770635</v>
       </c>
       <c r="D11" t="n">
-        <v>6.057273682377518</v>
+        <v>5.867267892275425</v>
       </c>
       <c r="E11" t="n">
-        <v>18.74124157078975</v>
+        <v>16.90674593717362</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.225812486647734</v>
+        <v>1.093274243449248</v>
       </c>
       <c r="C12" t="n">
-        <v>12.53640768895696</v>
+        <v>12.02219767937221</v>
       </c>
       <c r="D12" t="n">
-        <v>6.490184333832754</v>
+        <v>6.190046902477691</v>
       </c>
       <c r="E12" t="n">
-        <v>21.25240450943745</v>
+        <v>19.30551882529915</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.485556740942727</v>
+        <v>0.8629464145559037</v>
       </c>
       <c r="C13" t="n">
-        <v>14.42457436936547</v>
+        <v>11.4788003250716</v>
       </c>
       <c r="D13" t="n">
-        <v>6.810294285608448</v>
+        <v>5.599103506860409</v>
       </c>
       <c r="E13" t="n">
-        <v>23.72042539591665</v>
+        <v>17.94085024648791</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.44212847267631</v>
+        <v>0.9251008617117695</v>
       </c>
       <c r="C14" t="n">
-        <v>10.18549498688206</v>
+        <v>13.51336444987565</v>
       </c>
       <c r="D14" t="n">
-        <v>5.23641645248051</v>
+        <v>5.866924280578939</v>
       </c>
       <c r="E14" t="n">
-        <v>16.86403991203888</v>
+        <v>20.30538959216636</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.452839340129642</v>
+        <v>0.8834354891435346</v>
       </c>
       <c r="C15" t="n">
-        <v>11.06536673185918</v>
+        <v>14.59961919723953</v>
       </c>
       <c r="D15" t="n">
-        <v>5.169382719234537</v>
+        <v>5.844785869848174</v>
       </c>
       <c r="E15" t="n">
-        <v>17.68758879122336</v>
+        <v>21.32784055623124</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.665770599703733</v>
+        <v>0.9513626128003716</v>
       </c>
       <c r="C16" t="n">
-        <v>13.13685438781995</v>
+        <v>16.90929848120467</v>
       </c>
       <c r="D16" t="n">
-        <v>5.52162397804125</v>
+        <v>6.198872814338871</v>
       </c>
       <c r="E16" t="n">
-        <v>20.32424896556493</v>
+        <v>24.05953390834391</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.322031276015798</v>
+        <v>0.5603423196759096</v>
       </c>
       <c r="C17" t="n">
-        <v>12.07372961636812</v>
+        <v>12.43628904354647</v>
       </c>
       <c r="D17" t="n">
-        <v>5.056540638108409</v>
+        <v>5.121689415762228</v>
       </c>
       <c r="E17" t="n">
-        <v>18.45230153049233</v>
+        <v>18.11832077898461</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.494288728202943</v>
+        <v>0.4454483858479053</v>
       </c>
       <c r="C18" t="n">
-        <v>14.20442647637202</v>
+        <v>11.29699046772213</v>
       </c>
       <c r="D18" t="n">
-        <v>5.339666858536146</v>
+        <v>4.617395072521769</v>
       </c>
       <c r="E18" t="n">
-        <v>21.03838206311111</v>
+        <v>16.35983392609181</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.483479685979185</v>
+        <v>0.5147401388136452</v>
       </c>
       <c r="C19" t="n">
-        <v>15.29626736817307</v>
+        <v>14.00359034851425</v>
       </c>
       <c r="D19" t="n">
-        <v>5.364279273481615</v>
+        <v>5.016603141499649</v>
       </c>
       <c r="E19" t="n">
-        <v>22.14402632763387</v>
+        <v>19.53493362882754</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.634040513902476</v>
+        <v>0.5779254210589699</v>
       </c>
       <c r="C20" t="n">
-        <v>17.7208405859662</v>
+        <v>16.81451074035963</v>
       </c>
       <c r="D20" t="n">
-        <v>5.696316164534928</v>
+        <v>5.416979490245584</v>
       </c>
       <c r="E20" t="n">
-        <v>25.0511972644036</v>
+        <v>22.80941565166419</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9651561680450393</v>
+        <v>0.6311165116750621</v>
       </c>
       <c r="C21" t="n">
-        <v>13.13384042236791</v>
+        <v>19.64673505738717</v>
       </c>
       <c r="D21" t="n">
-        <v>4.718868515232719</v>
+        <v>5.805800668512533</v>
       </c>
       <c r="E21" t="n">
-        <v>18.81786510564567</v>
+        <v>26.08365223757476</v>
       </c>
     </row>
   </sheetData>
